--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N30_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>11.12033817221713</v>
+        <v>1.807054952985284</v>
       </c>
       <c r="D2" t="n">
-        <v>3.241306584707533</v>
+        <v>0.5267123200149741</v>
       </c>
       <c r="E2" t="n">
-        <v>11.67488246278382</v>
+        <v>1.89716840020237</v>
       </c>
       <c r="F2" t="n">
-        <v>14.60959052316072</v>
+        <v>2.374058460013617</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.01680932694344</v>
+        <v>5.202731515628309</v>
       </c>
       <c r="D3" t="n">
-        <v>32.03764358820982</v>
+        <v>5.206117083084097</v>
       </c>
       <c r="E3" t="n">
-        <v>11.67488246278382</v>
+        <v>1.89716840020237</v>
       </c>
       <c r="F3" t="n">
-        <v>14.60959052316072</v>
+        <v>2.374058460013617</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.36798479858022</v>
+        <v>6.234797529769286</v>
       </c>
       <c r="D4" t="n">
-        <v>45.99140257821139</v>
+        <v>7.473602918959352</v>
       </c>
       <c r="E4" t="n">
-        <v>11.67488246278382</v>
+        <v>1.89716840020237</v>
       </c>
       <c r="F4" t="n">
-        <v>14.60959052316072</v>
+        <v>2.374058460013617</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>45.51932639300014</v>
+        <v>7.396890538862523</v>
       </c>
       <c r="D5" t="n">
-        <v>14.74105639079819</v>
+        <v>2.395421663504707</v>
       </c>
       <c r="E5" t="n">
-        <v>11.67488246278382</v>
+        <v>1.89716840020237</v>
       </c>
       <c r="F5" t="n">
-        <v>14.60959052316072</v>
+        <v>2.374058460013617</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.45654562191104</v>
+        <v>4.299188663560545</v>
       </c>
       <c r="D6" t="n">
-        <v>25.70719157745397</v>
+        <v>4.17741863133627</v>
       </c>
       <c r="E6" t="n">
-        <v>11.67488246278382</v>
+        <v>1.89716840020237</v>
       </c>
       <c r="F6" t="n">
-        <v>14.60959052316072</v>
+        <v>2.374058460013617</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
